--- a/public/Indice biblioteca como sujeto colectivo.xlsx
+++ b/public/Indice biblioteca como sujeto colectivo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gesquive\Desktop\DOCTORADO - TESIS\Oficios para panel de expertos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Escritorio\WEB\pva\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BEC84B1-211F-4704-B14A-DBA47F0352B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4BCF9BC-BF1E-4310-99E5-795D67D6BAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" tabRatio="733" xr2:uid="{9323457E-9B47-4EF0-B2C9-B371339CBF67}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="733" xr2:uid="{9323457E-9B47-4EF0-B2C9-B371339CBF67}"/>
   </bookViews>
   <sheets>
     <sheet name="Bib. como sujeto colectivo" sheetId="2" r:id="rId1"/>
@@ -39,17 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="151">
   <si>
     <t xml:space="preserve">  La Biblioteca como Sujeto Colectivo</t>
   </si>
   <si>
-    <t xml:space="preserve">«un/el público» como un sujeto que representa los intereses de lo colectivo, sea una comunidad, la sociedad, las bibliotecas o el personal bibliotecario </t>
-  </si>
-  <si>
-    <t>Valora si la intervención del sujeto que representa  a la biblioteca se acerca más a lo colectivo que a lo individual</t>
-  </si>
-  <si>
     <t>EVALUACIÓN ÍNDICE</t>
   </si>
   <si>
@@ -119,77 +113,50 @@
     <t>SC1. Participación</t>
   </si>
   <si>
-    <t>Grado en que la comunidad interviene activamente en la configuración, toma de decisiones y aprovechamiento de la biblioteca, incidiendo de manera directa en su diseño, funcionamiento y evolución</t>
-  </si>
-  <si>
-    <t>La comunidad participa en el diseño físico, virtual y espacial de la biblioteca</t>
-  </si>
-  <si>
-    <t>Establece mecanismos de participación ciudadana en la toma de decisiones sobre  la biblioteca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utiliza la biblioteca para  propuestas, proyectos e iniciativas para el diseño o rediseño </t>
-  </si>
-  <si>
-    <t>SC2. Acciones como agente</t>
-  </si>
-  <si>
-    <t>Capacidad de la comunidad para ejercer influencia efectiva y deliberada en la gobernanza y evaluación de la biblioteca, expresando sus intereses, necesidades y propuestas.</t>
-  </si>
-  <si>
-    <t>La comunidad es consultada para el diseño y la planificación de programas y servicios.</t>
-  </si>
-  <si>
-    <t>Tiene voz en la gobernanza de la biblioteca y en decisiones estratégicas</t>
-  </si>
-  <si>
-    <t>Externa comentarios, necesidades y retroalimentación a  a través de sus plataformas o buzón de sugerencias</t>
-  </si>
-  <si>
-    <t>SC3. Donaciones</t>
-  </si>
-  <si>
-    <t>Contribuciones voluntarias de la comunidad que fortalecen los recursos, infraestructura y sostenibilidad de la biblioteca, tanto de manera directa como mediante la gestión de apoyos externos.</t>
-  </si>
-  <si>
-    <t>Contribuye con mobiliario, equipo o recursos para el espacio. Facilita locales o espacios para la biblioteca (comodato, préstamo, renta)</t>
-  </si>
-  <si>
-    <t>Busca apoyo de otras entidades para mejorar las condiciones de la biblioteca</t>
-  </si>
-  <si>
-    <t>Donaciones personales de libros</t>
-  </si>
-  <si>
-    <t>SC4. Proyección pública</t>
-  </si>
-  <si>
-    <t>Capacidad de la comunidad para visibilizar, posicionar y amplificar el valor de la biblioteca en el entorno social, promoviendo su reconocimiento como espacio de transformación comunitaria.</t>
-  </si>
-  <si>
-    <t>Difunde la biblioteca y sus condiciones en medios y redes.</t>
-  </si>
-  <si>
-    <t>Gestiona plataformas de expresión ciudadana convirtiendo a la biblioteca en un foro abierto</t>
-  </si>
-  <si>
-    <t>Crea bancos de testimonios que reflejan la mejora de la comunidad gracias a la biblioteca.</t>
-  </si>
-  <si>
-    <t>Evalúa Personal bibliotecario</t>
-  </si>
-  <si>
-    <t>Personal bibliotecario como agente</t>
-  </si>
-  <si>
-    <t>Formas de actuar y defender los intereses, derechos y necesidades de la comunidad, más allá del perfil de puesto.</t>
-  </si>
-  <si>
-    <t>¿Qué acciones realiza el  personal bibliotecario para mejorar el diseño de la biblioteca y su distribución espacial?</t>
-  </si>
-  <si>
-    <r>
-      <t>¿</t>
+    <t>Es la participación activa de la comunidad en la configuración biblioteca, incidiendo de manera directa en su diseño, funcionamiento y evolución.</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La comunidad participa en el diseño de los espacios físicos y virtuales de la biblioteca, para que respondan a sus necesidades y aspiraciones.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5.       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Participa como voluntariado en las gestiones desarrolladas por las biblioteca para ampliar su capacidad de servicio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11.</t>
     </r>
     <r>
       <rPr>
@@ -198,6 +165,224 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Manifiesta  opiniones, necesidades y retroalimentación a través de canales formales e informales (plataformas, buzones, redes). 12.       La comunidad participa en actividades públicas o de diálogo en la biblioteca.</t>
+    </r>
+  </si>
+  <si>
+    <t>SC2. Acciones como agente</t>
+  </si>
+  <si>
+    <t>Capacidad de la comunidad para ejercer influencia efectiva y deliberada en la gobernanza y evaluación de la biblioteca, expresando sus intereses, necesidades y propuestas.</t>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gestiona la participación  de la comunidad en procesos consultivos para el diseño de los espacios,  la planificación de programas, servicios y actividades.</t>
+    </r>
+  </si>
+  <si>
+    <t>6.       Establece mecanismos formales de participación ciudadana (comités, consultas, asambleas)  para incidir en decisiones sobre la biblioteca. .7.       La comunidad tiene voz y voto en la gobernanza de la biblioteca y en decisiones estratégicas. 8.       Las opiniones de la comunidad son tomadas en cuenta en la planificación programas y servicios.</t>
+  </si>
+  <si>
+    <r>
+      <t>13.       Emplea la biblioteca como base de operaciones para proponer, desarrollar e implementar proyectos e iniciativas que contribuyan a su mejora.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>14.       Desarrollan en la biblioteca actividades o proyectos impulsados por la comunidad.</t>
+    </r>
+  </si>
+  <si>
+    <t>SC3. Donaciones</t>
+  </si>
+  <si>
+    <t>Contribuciones voluntarias de la comunidad que fortalecen los recursos, infraestructura y sostenibilidad de la biblioteca, tanto de manera directa como mediante la gestión de apoyos externos.</t>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La comunidad contribuye con recursos (mobiliario, equipos, espacios físicos) que inciden en la configuración y funcionamiento del espacio bibliotecario.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">9.       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gestiona apoyos con otras entidades (públicas, privadas o comunitarias)  para mejorar las condiciones de la biblioteca</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hace donaciones individuales o colectivas, especialmente de libros u otros recursos, que enriquecen la oferta de la biblioteca.</t>
+    </r>
+  </si>
+  <si>
+    <t>SC4. Proyección pública</t>
+  </si>
+  <si>
+    <t>Capacidad de la comunidad para visibilizar, posicionar y amplificar el valor de la biblioteca en el entorno social, promoviendo su reconocimiento como espacio de transformación comunitaria.</t>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La comunidad difunde la biblioteca, sus servicios y condiciones a través de medios y redes, contribuyendo a su posicionamiento e identidad.</t>
+    </r>
+  </si>
+  <si>
+    <t>10. Gestiona plataformas de expresión ciudadana convirtiendo a la biblioteca en un foro abierto</t>
+  </si>
+  <si>
+    <r>
+      <t>16.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Genera y recopila  testimonios, narrativas y evidencias que muestran el impacto positivo de la biblioteca en la comunidad (visibiliza beneficios).</t>
+    </r>
+  </si>
+  <si>
+    <t>Evalúa Personal bibliotecario</t>
+  </si>
+  <si>
+    <t>Personal bibliotecario como agente</t>
+  </si>
+  <si>
+    <t>Formas de actuar y defender los intereses, derechos y necesidades de la comunidad, más allá del perfil de puesto.</t>
+  </si>
+  <si>
+    <t>¿Qué acciones realiza el  personal bibliotecario para mejorar el diseño de la biblioteca y su distribución espacial?</t>
+  </si>
+  <si>
+    <r>
+      <t>¿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>Qué acciones realiza el  personal bibliotecario en beneficio de la comunidad que flexibiliza la gobernanza de la biblioteca?</t>
     </r>
   </si>
@@ -208,16 +393,79 @@
     <t>SB1. Procesos participativos (Co-creación)</t>
   </si>
   <si>
-    <t>Capacidad del personal bibliotecario para involucrar activamente a la comunidad en la toma de decisiones, promoviendo procesos colaborativos que influyen en el diseño, gestión y uso de la biblioteca.</t>
-  </si>
-  <si>
-    <t>Realiza consultas comunitarias para mejorar el diseño físico y espacial</t>
-  </si>
-  <si>
-    <t>Crea comités o consejos ciudadanos que democratizan decisiones sobre presupuesto, colecciones y servicios.</t>
-  </si>
-  <si>
-    <t>Mantiene plataformas de expresión ciudadana para compartir ideas, propuestas o denuncias, convirtiendo a la biblioteca en un foro abierto</t>
+    <t>Acciones del personal bibliotecario para involucrar activamente a la comunidad en la toma de decisiones, promoviendo procesos colaborativos que influyen en el diseño, gestión y uso de la biblioteca.</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Realiza consultas comunitarias para mejorar el diseño físico y espacial</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Crea comités o consejos ciudadanos que democratizan decisiones sobre presupuesto, colecciones y servicios.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mantiene plataformas de expresión ciudadana para compartir ideas, propuestas o denuncias, convirtiendo a la biblioteca en un foro abierto</t>
+    </r>
   </si>
   <si>
     <t>SB2. Creación de públicos</t>
@@ -226,13 +474,76 @@
     <t>Conjunto de acciones orientadas a diversificar y ampliar la base de usuarios, integrando a públicos no tradicionales mediante el rediseño de espacios, servicios y actividades relevantes.</t>
   </si>
   <si>
-    <t>Adapta/Diseña espacios polivalentes que se adecuan a usuarios no tradicionales (zonas de ruido, makerspaces, recreación).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promueve diferentes usos de las instalaciones para reuniones abiertas con vecinos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organiza eventos, talleres o grupos de discusión sobre asuntos cívicos, sociales, económicos o políticos </t>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adapta/Diseña espacios polivalentes que se adecuan a usuarios no tradicionales (zonas de ruido, makerspaces, recreación).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Promueve diferentes usos de las instalaciones para reuniones abiertas con vecinos </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>18.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Organiza eventos, talleres o grupos de discusión sobre asuntos cívicos, sociales, económicos o políticos </t>
+    </r>
   </si>
   <si>
     <t>SB3. Laboratorios sociales</t>
@@ -241,13 +552,76 @@
     <t>Capacidad del personal para convertir la biblioteca en un espacio de experimentación, innovación y creación colectiva donde la comunidad desarrolla soluciones a problemáticas sociales y culturales</t>
   </si>
   <si>
-    <t xml:space="preserve">Planifica áreas de experimentación  que invitan a la creación colectiva (Makerspaces) </t>
-  </si>
-  <si>
-    <t>Facilita/Promueve usos diversos de las salas para reuniones vecinales y asambleas de la comunidad</t>
-  </si>
-  <si>
-    <t>Convierte la biblioteca en un espacio de creación y proyectos cívicos o culturales.</t>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Planifica áreas de experimentación  que invitan a la creación colectiva (Makerspaces) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Facilita/Promueve usos diversos de las salas para reuniones vecinales y asambleas de la comunidad</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>19.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Convierte la biblioteca en un espacio de creación y proyectos cívicos o culturales.</t>
+    </r>
   </si>
   <si>
     <t>SB4. Activismo del espacio </t>
@@ -256,13 +630,76 @@
     <t>Uso estratégico del espacio bibliotecario (interno y externo) como herramienta de transformación social, orientado a atraer nuevos públicos y activar dinámicas comunitarias.</t>
   </si>
   <si>
-    <t>Implementa estrategias de urbanismo (en la fachada o alrededores) para atraer a no-usuarios</t>
-  </si>
-  <si>
-    <t>Diseña programas alternativos para activar el espacio exterior de la bibliotetc</t>
-  </si>
-  <si>
-    <t>Promueve actividades fuera del edificio de la biblioteca.</t>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implementa estrategias de urbanismo (en la fachada o alrededores) para atraer a no-usuarios</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Diseña programas alternativos para activar el espacio exterior de la biblioteca</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>20.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Promueve actividades fuera del edificio de la biblioteca.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">SB5. Colaboración </t>
@@ -271,28 +708,146 @@
     <t>Habilidad del personal bibliotecario para establecer alianzas estratégicas con actores locales, organizaciones y redes profesionales que fortalecen el impacto social y político de la biblioteca.</t>
   </si>
   <si>
-    <t xml:space="preserve">Busca patrocinios o aliados locales para re/diseñar la biblioteca </t>
-  </si>
-  <si>
-    <t>Participa en asociaciones y redes profesionistas interdisciplinas para incidir en políticas públicas</t>
-  </si>
-  <si>
-    <t>Crea alianzas con líderes comunitarios para integrar la biblioteca en la vida del barrio</t>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Busca patrocinios o aliados locales para re/diseñar la biblioteca </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>13.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Participa en asociaciones y redes profesionistas interdisciplinas para incidir en políticas públicas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>21.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Crea alianzas con líderes comunitarios para integrar la biblioteca en la vida del barrio</t>
+    </r>
   </si>
   <si>
     <t>SB6. Proyección pública</t>
   </si>
   <si>
-    <t>Capacidad del personal para posicionar la biblioteca como un actor relevante en el espacio público mediante estrategias de comunicación, visibilidad y liderazgo cultural.</t>
-  </si>
-  <si>
-    <t>Proyecta  a la biblioteca en redes sociodigitales y medios de comunicación</t>
-  </si>
-  <si>
-    <t>Gestiona la proyección pública de las bibliotecas en diversos medios</t>
-  </si>
-  <si>
-    <t>Proyecta su imagen profesional como referente cultural y bibliotecario. en redes sociodigitales y medios de comunicación</t>
+    <t xml:space="preserve">Proyección pública e influencia personal del bibliotecario que impacta directamente en la imagen de la biblioteca </t>
+  </si>
+  <si>
+    <r>
+      <t>6. Traduce su prestigio y posicionamiento público en cómo se proyecta y transforma el espacio físico, reflejando su visión profesional y dando visibilidad institucional.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>14. Utiliza su liderazgo y reconocimiento público para negociar recursos, influir en la toma de decisiones políticas y flexibilizar la gobernanza de la biblioteca.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>22.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proyecta su imagen  como referente cultural y bibliotecario, en redes sociodigitales y medios de comunicación</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con lo que refleja el liderazgo cultural de la institución </t>
+    </r>
   </si>
   <si>
     <t>SB7. Narrativas de valor</t>
@@ -301,13 +856,76 @@
     <t>Capacidad de construir, comunicar y evidenciar el impacto social de la biblioteca a través de relatos, indicadores y representaciones que reflejan su valor en la comunidad.</t>
   </si>
   <si>
-    <t>Diseña campañas visuales que muestran a la biblioteca como un refugio o centro social.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adapta métricas internas para valorar el impacto social por encima de la simple estadística. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhibe historias y experiencias que reflejan problemas y soluciones de la comunidad </t>
+    <r>
+      <t>7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Diseña campañas visuales que muestran a la biblioteca como un lugar para múltiples propósitos .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Adapta métricas internas para valorar el impacto social por encima de la simple estadística. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>23.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Exhibe historias y experiencias que reflejan problemas y soluciones de la comunidad </t>
+    </r>
   </si>
   <si>
     <t>SB8. Implicación/intervención publica</t>
@@ -316,13 +934,76 @@
     <t>Nivel de compromiso del personal bibliotecario en la defensa de derechos, inclusión social y participación en causas comunitarias más allá de sus funciones tradicionales.</t>
   </si>
   <si>
-    <t>Defiende espacios neutrales y seguros para grupos vulnerables.</t>
-  </si>
-  <si>
-    <t>Participar en asociaciones y redes</t>
-  </si>
-  <si>
-    <t>Participa en movimientos sociales contemporáneos y redes de activismo locales</t>
+    <r>
+      <t>8.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Defiende espacios neutrales y seguros para grupos vulnerables.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Participar en asociaciones y redes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>24.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Participa en movimientos sociales contemporáneos y redes de activismo locales</t>
+    </r>
   </si>
   <si>
     <t>Evalúa Equipo de invesigación</t>
@@ -337,7 +1018,7 @@
     <t>Formas de actuar para legitimar, normar y defender los intereses de la sociedad, las bibliotecas y del personal bibliotecario</t>
   </si>
   <si>
-    <t>¿Qué acciones realizan las ILN para establecer  diseño y rediseño del espacio de la biblioteca?</t>
+    <t>¿Qué acciones realizan las ILN para establecer un diseño ideal del espacio de la biblioteca?</t>
   </si>
   <si>
     <t>¿Qué acciones realizan las ILN para legitimar y normar diversos tipos de bibliotecas?</t>
@@ -352,13 +1033,76 @@
     <t>Conjunto de declaraciones y posicionamientos institucionales que orientan el diseño, gestión y rol social de las bibliotecas y de su personal (Declaraciones manifiestos)</t>
   </si>
   <si>
-    <t> Declaraciones y manifiestos que presionan el diseño de la biblioteca</t>
-  </si>
-  <si>
-    <t>Declaraciones y manifiestos que dictan pautas e ideales que una biblioteca debe cumplir</t>
-  </si>
-  <si>
-    <t>Declaraciones  y manifiestos que definen el perfil profesional y los derechos del personal bibliotecario</t>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> Emiten declaraciones y manifiestos que presionan el diseño de la biblioteca</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>       Emiten d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eclaraciones y manifiestos que dictan pautas e ideales que una biblioteca debe cumplir</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>23.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>       Emien d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eclaraciones  y manifiestos que definen el perfil profesional y los derechos del personal bibliotecario</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">SI2. Decisiones y acuerdos </t>
@@ -367,13 +1111,76 @@
     <t>Resoluciones y convenios formales (acuerdos, convenios, resoluciones) que establecen marcos de acción para bibliotecas, sus servicios, personal bibliotecario  y  usuarios.</t>
   </si>
   <si>
-    <t>Resoluciones, convenios y acuerdos técnicos que orientan la planificación, construcción, adecuación y rediseño de los espacios bibliotecarios</t>
-  </si>
-  <si>
-    <t>Formaliza acuerdos, conveios o resoluciones sobre las formas de gestión y presación de los servicios.</t>
-  </si>
-  <si>
-    <t> Acuerdos, convenios, resoluciones  sobre derechos de autor, libre acceso a la información y ética profesional</t>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Establecen resoluciones, convenios y acuerdos que orientan la planificación, construcción, adecuación y rediseño de los espacios bibliotecarios</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>13.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Formalizan acuerdos, convenios o resoluciones sobre las formas de gestión y prestación de los servicios.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>24.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>  Formalizan acuerdos, convenios, resoluciones  sobre derechos de autor, libre acceso a la información y ética profesional</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">SI3. Compromisos formales </t>
@@ -382,13 +1189,76 @@
     <t>Los compromisos institucionales o gubernamentales que marcan una hoja de ruta con objetivos específicos que deben cumplirse en un tiempo determinado. (agendas, planes de trabajo)</t>
   </si>
   <si>
-    <t> Compromisos, agendas o  planes para adecuar la infraestructura física o remodelación tecnológica.</t>
-  </si>
-  <si>
-    <t>Establece agendas o planes para  alinear el trabajo bibliotecario con metas globales de desarrollo.</t>
-  </si>
-  <si>
-    <t>Impulsa planes y compromisos para fortalecer la inclusión, alfabetización informacional, participación comunitaria y desarrollo profesional del personal bibliotecario.</t>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> Establecen compromisos, agendas o  planes para adecuar la infraestructura física o remodelación tecnológica.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>14.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Establecen agendas o planes para  alinear el trabajo bibliotecario con metas globales de desarrollo.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>25.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Impulsan planes y compromisos para fortalecer la inclusión, alfabetización informacional, participación comunitaria y desarrollo profesional del personal bibliotecario.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">SI4. Regulación </t>
@@ -397,13 +1267,76 @@
     <t>Ecosisetma legal y ético: Conjunto de leyes, normas y disposiciones técnicas que regulan el funcionamiento, infraestructura, servicios y comportamiento dentro de las bibliotecas.</t>
   </si>
   <si>
-    <t>Propone o establece normas técnicas de edificación  diseño de bibliotecas</t>
-  </si>
-  <si>
-    <t>Emite leyes, políticas, reglamentos o normativas públicas para la gesión biblioetcaria</t>
-  </si>
-  <si>
-    <t>Establece código de ética profesional y cartas de derechos para las personas usuarias</t>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proponen o establecen normas técnicas de edificación y diseño de bibliotecas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Emite leyes, políticas, reglamentos o normativas públicas para la gestión bibliotecaria</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>26.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Establece código de ética profesional y cartas de derechos para las personas usuarias</t>
+    </r>
   </si>
   <si>
     <t>SI5. Rendición de  cuentas</t>
@@ -412,13 +1345,76 @@
     <t>Obligaciones institucionales explícitas. Procesos de transparencia mediante los cuales se reportan resultados, uso de recursos y desempeño institucional.</t>
   </si>
   <si>
-    <t>Publica informes de las condiciones de las instalaciones físicas y virtuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Crea informes de actividades, estadísticas de uso y estados financieros y  esta abierta al escrutinio público.</t>
-  </si>
-  <si>
-    <t>Comunica la gestión de la biblioteca a la comunidad y a los tomadores de decisiones</t>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Publican informes de las condiciones de las instalaciones físicas y virtuales</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Crean informes de actividades, estadísticas de uso y estados financieros y  está abierta al escrutinio público.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>27.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Comunican la gestión de la biblioteca a la comunidad y a los tomadores de decisiones</t>
+    </r>
   </si>
   <si>
     <t>SI6. Auditorías </t>
@@ -427,13 +1423,76 @@
     <t>Mecanismos de evaluación sistemática que revisan el desempeño, uso de recursos, impacto y cumplimiento normativo de las bibliotecas.</t>
   </si>
   <si>
-    <t> Auditorías de inversión en infraestructura y equipamiento</t>
-  </si>
-  <si>
-    <t>Realiza auditorías administrativas y evaluaciones de impacto institucional.</t>
-  </si>
-  <si>
-    <t>Lleva a cabo estudios de usuarios y uso de servicios.</t>
+    <r>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>       Realizan s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Auditorías de inversión en infraestructura y equipamiento</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Realizan auditorías administrativas y evaluaciones de impacto institucional.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>28.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Llevan a cabo estudios de usuarios y uso de servicios.</t>
+    </r>
   </si>
   <si>
     <t>SI7. Certificaciones</t>
@@ -442,13 +1501,76 @@
     <t>Reconocimientos formales que validan el cumplimiento de estándares de calidad en infraestructura, gestión y profesionalización del personal bibliotecario.</t>
   </si>
   <si>
-    <t>Certificaciones de calidad del espacio físico, instalaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certificaciones de calidad para la gestión de los servicios  </t>
-  </si>
-  <si>
-    <t>Certifica competencias y profesionalización del personal bibliotecario.</t>
+    <r>
+      <t>7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>     Otorgan c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ertificaciones de calidad del espacio físico, instalaciones.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">18.   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Otorgan c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ertificaciones de calidad para la gestión de los servicios  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>29.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Certifican competencias y profesionalización del personal bibliotecario.</t>
+    </r>
   </si>
   <si>
     <t>SI8. Estándares</t>
@@ -457,13 +1579,76 @@
     <t>Criterios técnicos y operativos que establecen niveles mínimos o deseables de calidad en el diseño, servicios, accesibilidad y experiencia en las bibliotecas.</t>
   </si>
   <si>
-    <t>Estándares de diseño, construcción, accesibilidad, seguridad y sostenibilidad arquitectónica.</t>
-  </si>
-  <si>
-    <t>Promueve los estándares de seguridad, accesibilidad y tecnología para los servicios. Normalizar procesos técnicos (catalogación, preservación, datos).</t>
-  </si>
-  <si>
-    <t>Define estándares de calidad en la atención, uso de servicios, experiencia del usuario y acceso inclusivo a la información.</t>
+    <r>
+      <t>8.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>       Establecen e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stándares de diseño, construcción, accesibilidad, seguridad y sostenibilidad arquitectónica.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>19.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Establecen estándares de seguridad, accesibilidad y tecnología para los servicios. Normalizar procesos técnicos (catalogación, preservación, datos).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>30.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Establecen estándares de calidad en la atención, uso de servicios, experiencia del usuario y acceso inclusivo a la información.</t>
+    </r>
   </si>
   <si>
     <t>SI9. Cooperación</t>
@@ -472,28 +1657,91 @@
     <t>Acciones de articulación institucional que fomentan la colaboración entre bibliotecas, organizaciones y comunidad para fortalecer su desarrollo e impacto.</t>
   </si>
   <si>
-    <t>Colabora con agrupacciones de profesionales de la arquitectura, diseño y urbanismos</t>
-  </si>
-  <si>
-    <t>Crea, participa en redes profesionales y asociaciones de bibliotecas.</t>
-  </si>
-  <si>
-    <t> Crea o paricipa en comités de vecinos, juntas vecinales, escuelas u otras entidades.</t>
+    <t>9.   Colaboran con agrupaciones de profesionales de la arquitectura, diseño y urbanismo para el diseño de los espacios bibliotecarios.</t>
+  </si>
+  <si>
+    <t>20. Crean y participan en redes de profesionales de la información y asociaciones de bibliotecas.</t>
+  </si>
+  <si>
+    <t>31. Crean y participan en comités de vecinos, juntas vecinales, escuelas u otras entidades.</t>
   </si>
   <si>
     <t>SI10. Recomendaciones operativas</t>
   </si>
   <si>
-    <t>Guías prácticas  directrices  que indican cómo se deberían hacer las cosas. Son recomendaciones técnicas para la gestión diaria.</t>
-  </si>
-  <si>
-    <t>Establece guías o directrices para orientar el diseño de espacios.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Establece guías o directrices para orientar el diseño de servicios y colecciones. </t>
-  </si>
-  <si>
-    <t>Emite recomendaciones sobre atención a usuarios, mediación lectora, accesibilidad, uso ético de la información y buenas prácticas del personal bibliotecario.</t>
+    <t>Guías prácticas y directrices  que indican cómo se deberían hacer las cosas. Son recomendaciones técnicas para la gestión diaria.</t>
+  </si>
+  <si>
+    <r>
+      <t>10.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Establecen guías o directrices para orientar el diseño de espacios.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>21.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Establecen guías o directrices para orientar el diseño de servicios y colecciones. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>32.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Emiten recomendaciones sobre atención a usuarios, mediación lectora, accesibilidad, uso ético de la información y buenas prácticas del personal bibliotecario.</t>
+    </r>
   </si>
   <si>
     <t>SI11. Reconocimientos</t>
@@ -502,20 +1750,80 @@
     <t>Distinciones, premios o menciones institucionales que valoran las buenas prácticas, innovación, trayectoria y aportes de bibliotecas y personal bibliotecario.</t>
   </si>
   <si>
-    <t>Reconoce proyectos destacados de diseño, innovación y adecuación de espacios bibliotecarios.</t>
-  </si>
-  <si>
-    <t>Emite reconocimientos a las bibliotecas por gestiones ejemplares</t>
-  </si>
-  <si>
-    <t>Emite reconocimientos al personal bibliotecario por su desempeño o trayectoria.</t>
+    <r>
+      <t>11.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reconocen proyectos destacados de diseño, innovación y adecuación de espacios bibliotecarios.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>22.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Emiten reconocimientos a las bibliotecas por gestiones ejemplares</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">33.     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Emiten reconocimientos al personal bibliotecario por su desempeño o trayectoria.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,8 +1944,55 @@
       <name val="Trade Gothic Next Heavy"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Garamond"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -670,12 +2025,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -686,14 +2035,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="39">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -732,19 +2075,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -776,13 +2106,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -797,10 +2127,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -812,68 +2142,10 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -983,32 +2255,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1027,6 +2273,81 @@
       </left>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1037,8 +2358,23 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1047,70 +2383,8 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -1126,6 +2400,58 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1139,377 +2465,320 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1531,25 +2800,75 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>441831</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>73959</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>972961</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>125568</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Imagen 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F213E28E-2955-42C5-8C4A-F016ACFDD80E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="441831" y="509387"/>
+          <a:ext cx="531130" cy="544668"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>321</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>56990</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2074690</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>102454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1210235</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>448875</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>363710</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="6" name="Grupo 5">
+        <xdr:cNvPr id="71" name="Grupo 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F27EC88B-5C47-4729-99B5-411EB4717D24}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FA12DD-1E64-4B4F-9145-CE277F570D1F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1557,18 +2876,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648521" y="2171540"/>
-          <a:ext cx="1171814" cy="391885"/>
+          <a:off x="4647801" y="11135579"/>
+          <a:ext cx="1306" cy="261256"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="961027"/>
+          <a:chExt cx="2836472" cy="795328"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="Signo menos 6">
+          <xdr:cNvPr id="72" name="Signo menos 71">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79D9E9D0-CA3B-4A54-ABA8-F57987025CF8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BA66669-2640-4B22-9CBC-06A1B7C0EDF1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1617,10 +2936,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="Signo más 7">
+          <xdr:cNvPr id="73" name="Signo más 72">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFFEFD8B-8907-4F00-AE27-CD93D3253483}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7444876-2106-4ED5-BABD-A3BADF58C373}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1669,10 +2988,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="9" name="Imagen 8">
+          <xdr:cNvPr id="74" name="Imagen 73">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83BB8691-8682-49DE-B547-28DFC8B83087}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07447FD3-681C-4DD2-8109-5EB075CF9427}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1681,7 +3000,188 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700779" y="132100"/>
+            <a:ext cx="2308099" cy="795328"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>31880</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>60650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1169438</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>435430</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="135" name="Grupo 134">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA24FAB1-D9B7-4641-A236-9229FA8D2ECC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4680987" y="2158418"/>
+          <a:ext cx="1089933" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="136" name="Signo menos 135">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A63EE9E6-D85A-4970-BC70-6E085697F121}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="137" name="Signo más 136">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D853C075-F881-4A73-B08E-FB96079F2368}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="138" name="Imagen 137">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45FD5011-E222-4F8C-97E4-43D974E8A120}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1715,22 +3215,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>10885</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>82925</xdr:rowOff>
+      <xdr:colOff>6480</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>116633</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1110343</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>344181</xdr:rowOff>
+      <xdr:colOff>1144038</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>491413</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="10" name="Grupo 9">
+        <xdr:cNvPr id="139" name="Grupo 138">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C36DDFF2-772C-4FBA-AACD-7718E2F42E09}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F0F180F-FE30-4DEA-89E4-88527862A8CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1738,18 +3238,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4659085" y="6321800"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4655587" y="2917437"/>
+          <a:ext cx="1118508" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="Signo menos 10">
+          <xdr:cNvPr id="140" name="Signo menos 139">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6BA51AC-1269-451B-A63C-0EC91600C27B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C79283E-3EAA-49D3-ABBF-3B3201C7C452}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1798,10 +3298,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Signo más 11">
+          <xdr:cNvPr id="141" name="Signo más 140">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D10C40AD-9F18-47D6-B223-BD854965E009}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5118209-A367-4EB6-B2DB-6C770A108F49}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1850,191 +3350,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="13" name="Imagen 12">
+          <xdr:cNvPr id="142" name="Imagen 141">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73521564-6E34-45BD-BBAE-FFE08A5EF09D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
-          <a:stretch/>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>37605</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>22762</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1175163</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>327561</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="Grupo 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B074E5C-931A-495C-A3F4-8DBFAE86A808}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4685805" y="12271912"/>
-          <a:ext cx="1137558" cy="304799"/>
-          <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="961027"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="Signo menos 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D763F9E5-F59D-47D5-90C0-5C1EC72E92B0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="393577" y="361215"/>
-            <a:ext cx="341454" cy="208344"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathMinus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="Signo más 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63247691-C107-4ED5-84CE-C34450A6727E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2993194" y="366696"/>
-            <a:ext cx="236855" cy="288924"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathPlus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="00B050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="17" name="Imagen 16">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C42CFDC-036F-4960-B508-24A8E57A25FA}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35FD4DDD-455D-4058-87A7-C0CE9B1C885B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2044,237 +3363,6 @@
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
           <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
-          <a:stretch/>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="700778" y="132100"/>
-            <a:ext cx="2308100" cy="961027"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>441831</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>73959</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>972961</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>125568</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Imagen 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F213E28E-2955-42C5-8C4A-F016ACFDD80E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="441831" y="509387"/>
-          <a:ext cx="531130" cy="544668"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2061883</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>134471</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1120588</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>526356</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="18" name="Grupo 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{654C05C3-D892-44C8-A571-8E154E9AF25A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4652683" y="2772896"/>
-          <a:ext cx="1116105" cy="391885"/>
-          <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="961027"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Signo menos 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4E8981F-152E-4356-9C0B-D7003ACEDB41}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="393577" y="361215"/>
-            <a:ext cx="341454" cy="208344"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathMinus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Signo más 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53C88560-805D-4778-8BBC-3201D9824C43}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2993194" y="366696"/>
-            <a:ext cx="236855" cy="288924"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathPlus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="00B050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="21" name="Imagen 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF2C595F-A0BD-4CE0-AE08-03BCE715CD5A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2307,23 +3395,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2068287</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19439</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>153681</xdr:rowOff>
+      <xdr:rowOff>84234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1139797</xdr:colOff>
+      <xdr:colOff>1156997</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>545566</xdr:rowOff>
+      <xdr:rowOff>459014</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="22" name="Grupo 21">
+        <xdr:cNvPr id="143" name="Grupo 142">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B03E94C-A6AD-45D3-9854-3D6559476650}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B498386-C888-4E08-A2D2-9140A27D7B87}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2331,18 +3419,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4649562" y="3373131"/>
-          <a:ext cx="1138435" cy="391885"/>
+          <a:off x="4668546" y="3746823"/>
+          <a:ext cx="1108983" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
           <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="24" name="Signo menos 23">
+          <xdr:cNvPr id="144" name="Signo menos 143">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD25E1F1-C456-45A8-95DD-8480F67FD366}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8962DA5B-2930-401D-A9ED-C0FEE7B6B7B4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2391,10 +3479,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="Signo más 24">
+          <xdr:cNvPr id="145" name="Signo más 144">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7FC1EAA-A37C-44A8-98AE-3E48822BEAAC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3B300A-BBA2-4A32-B442-1F52A036C828}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2443,10 +3531,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="26" name="Imagen 25">
+          <xdr:cNvPr id="146" name="Imagen 145">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43088D31-18A2-4ABF-8714-7797BA9A18DB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F29E1FFF-EA23-455C-82B2-30B01DAF9D09}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2455,7 +3543,369 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>12960</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>103674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1150518</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>478454</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="147" name="Grupo 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32AA7C82-AC12-4928-93CB-68890969CD9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4662067" y="4333228"/>
+          <a:ext cx="1108983" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="148" name="Signo menos 147">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E3744E6-9F8C-4A0B-AA46-090370130FAC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="149" name="Signo más 148">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1400C068-A7B1-4416-9C9B-DC5CC648C518}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="150" name="Imagen 149">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{215DCE31-0082-43E1-B4DF-D4672D2771B9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>31880</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>80089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1169438</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>454869</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="151" name="Grupo 150">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8902ECB7-572B-42EA-B70C-2E59735D324C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4680987" y="6826964"/>
+          <a:ext cx="1089933" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="152" name="Signo menos 151">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01BDC537-5A01-4EFA-90FA-B969DA62A147}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="153" name="Signo más 152">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6EE9725-B7DF-4EAE-8CD5-5748E5C6DE3B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="154" name="Imagen 153">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{399B17AE-0CCD-4293-B75B-BBBBF294FE1D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2490,21 +3940,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>96050</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>77755</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1159008</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>487935</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>452535</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="27" name="Grupo 26">
+        <xdr:cNvPr id="159" name="Grupo 158">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11C95632-6768-496A-A675-03C8604B0EAA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57E71458-EA2E-432D-83AB-592D492FEF22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2512,18 +3962,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648200" y="3877475"/>
-          <a:ext cx="1159008" cy="391885"/>
+          <a:off x="4649107" y="7901862"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
           <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="Signo menos 27">
+          <xdr:cNvPr id="160" name="Signo menos 159">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECE5D978-167E-4B89-9CBC-5F8C40EE646D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12520EA4-9BA1-4E5F-8BE5-ECB73E8C6D77}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2572,10 +4022,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="Signo más 28">
+          <xdr:cNvPr id="161" name="Signo más 160">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AE03A2F-E1C3-45BE-A696-511817BABE79}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98CA0D53-8DFF-440C-B6A7-55F7D4C707DD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2624,10 +4074,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="30" name="Imagen 29">
+          <xdr:cNvPr id="162" name="Imagen 161">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AADFEF90-9194-41C5-9EF8-D12E38DC3B96}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5589747C-E480-45CA-9196-545CF598030C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2636,7 +4086,188 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2073469</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>161990</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1131078</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>536770</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="163" name="Grupo 162">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842FCDFF-477E-4FFC-95B3-905345645E97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4646580" y="8643776"/>
+          <a:ext cx="1124080" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="164" name="Signo menos 163">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6955DDA7-0BB5-4389-AD91-D988A9804EAF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="165" name="Signo más 164">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB46B8CD-89ED-465E-AB93-7906A348A09D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="166" name="Imagen 165">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46F865B6-B351-4709-BB0B-9E597FC2981E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2670,22 +4301,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>10885</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>97972</xdr:rowOff>
+      <xdr:colOff>31880</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>60650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1148443</xdr:colOff>
+      <xdr:colOff>1169438</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>402771</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="31" name="Grupo 30">
+        <xdr:cNvPr id="167" name="Grupo 166">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{332EE9DC-5170-464E-A36B-D176CD99CBDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{022531E8-C777-4E64-A6A2-DDE8F2B2C062}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2693,18 +4324,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4659085" y="12690022"/>
-          <a:ext cx="1137558" cy="304799"/>
+          <a:off x="4680987" y="13225561"/>
+          <a:ext cx="1089933" cy="438279"/>
           <a:chOff x="393577" y="132100"/>
           <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="32" name="Signo menos 31">
+          <xdr:cNvPr id="168" name="Signo menos 167">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B9E706B-DFFE-485A-926F-7BF8A04FB85B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC1316EA-C2A3-4706-A52B-2E2A71355E54}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2753,10 +4384,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="33" name="Signo más 32">
+          <xdr:cNvPr id="169" name="Signo más 168">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0328B9AE-F6EB-4464-A916-36993EB13947}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{843928E9-08AC-41D4-832C-2C171AC1868E}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2805,10 +4436,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="34" name="Imagen 33">
+          <xdr:cNvPr id="170" name="Imagen 169">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20519AF4-A25D-4F45-8D26-5F3612F8238F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BEB2B8A-E6D5-49BE-BBC0-DE6EFF88D225}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2817,7 +4448,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2851,22 +4482,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>5443</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>87086</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1143001</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>391885</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>420137</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="43" name="Grupo 42">
+        <xdr:cNvPr id="171" name="Grupo 170">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3003A907-F176-4B11-BACC-4D2DC88F0A2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74B297C5-C0B3-458D-A836-1D1D5B2BA64F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2874,18 +4505,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4653643" y="13136336"/>
-          <a:ext cx="1137558" cy="304799"/>
+          <a:off x="4649107" y="13709196"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
           <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="44" name="Signo menos 43">
+          <xdr:cNvPr id="172" name="Signo menos 171">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{359516DC-284D-4782-A67F-FDCD878E7403}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7BD9A9E-B703-4DE0-A778-04572C103319}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2934,10 +4565,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="45" name="Signo más 44">
+          <xdr:cNvPr id="173" name="Signo más 172">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3572A7EC-E1DB-488B-A256-79365DB84BC0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0393146-C089-44F4-BDCE-DA08C0E4C4A0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2986,10 +4617,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="46" name="Imagen 45">
+          <xdr:cNvPr id="174" name="Imagen 173">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3140117E-9705-4967-8DA6-EC7923084FFB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{699B8444-0146-4A1A-98C8-624B37A27FF3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3032,22 +4663,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>146957</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>103674</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1164772</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>451756</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>478454</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="47" name="Grupo 46">
+        <xdr:cNvPr id="175" name="Grupo 174">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98582696-8937-4B51-9FC9-0060649BECE1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88E47E57-4053-4F41-B33B-E462B1A32C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3055,18 +4686,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4675414" y="13653407"/>
-          <a:ext cx="1137558" cy="304799"/>
+          <a:off x="4649107" y="14379835"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
           <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="48" name="Signo menos 47">
+          <xdr:cNvPr id="176" name="Signo menos 175">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10D29E1-6B5F-4FB7-8467-D8453A505C1F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE71CB69-CE72-4A22-8EC8-72A691FA9B45}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3115,10 +4746,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="49" name="Signo más 48">
+          <xdr:cNvPr id="177" name="Signo más 176">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27023443-267F-47EF-8D2A-8B7EB4B1907F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65AC491F-4759-4A6D-BCB0-9F399295720C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3167,10 +4798,191 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="50" name="Imagen 49">
+          <xdr:cNvPr id="178" name="Imagen 177">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADD914C9-6C12-4DDF-BFF3-5E5330072E1F}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C8302B5-42DE-4905-B7BA-0C4815C8DEE8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>77755</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>452535</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="179" name="Grupo 178">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{065E97E6-D8D1-477C-8871-9FD97661D71C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4649107" y="15079630"/>
+          <a:ext cx="1128033" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="180" name="Signo menos 179">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0665A6D2-5377-425B-AA97-382DA3490CCB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="181" name="Signo más 180">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF3861E3-3A53-4ABB-BA54-198C17D0648F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="182" name="Imagen 181">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DBBC1E8-3DB4-4B7F-8BF8-7587EEB51084}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3215,20 +5027,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>64033</xdr:rowOff>
+      <xdr:rowOff>77756</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
+      <xdr:colOff>1137558</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>325289</xdr:rowOff>
+      <xdr:rowOff>452536</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="51" name="Grupo 50">
+        <xdr:cNvPr id="183" name="Grupo 182">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93CEAF1C-BB34-4CDD-84D9-F0BCA9D1A397}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8327DB99-F2C9-437B-AA27-3E0669087711}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3236,18 +5048,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648200" y="6855358"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="7380256"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="52" name="Signo menos 51">
+          <xdr:cNvPr id="184" name="Signo menos 183">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C32E809-8AEA-4C71-B24F-161BC4C90384}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE8D9D64-A105-43BE-AC5F-860BA239F2CB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3296,10 +5108,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="53" name="Signo más 52">
+          <xdr:cNvPr id="185" name="Signo más 184">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EE35BCA-9FDE-45A0-A7A2-4E509B327299}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7523F8C4-222A-4D66-892C-EB6FD871D955}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3348,10 +5160,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="54" name="Imagen 53">
+          <xdr:cNvPr id="186" name="Imagen 185">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D74E5C14-9449-49F4-832C-07C5F7B7D593}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E3FA91A-61D1-4080-A5A2-EA17BDFCFCA5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3360,20 +5172,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3395,21 +5207,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76840</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>338096</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>510852</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="55" name="Grupo 54">
+        <xdr:cNvPr id="187" name="Grupo 186">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A63C056-FCC7-4673-B7EC-BAE396D55DF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50E0BDC8-3403-45F3-8A75-583ED6897881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3417,18 +5229,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648200" y="7392040"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="9275536"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="56" name="Signo menos 55">
+          <xdr:cNvPr id="188" name="Signo menos 187">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{012AB806-0F4E-4DE7-85DF-055238D80935}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1935C674-FF17-4EB3-8AD4-9AB7F4EE77B8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3477,10 +5289,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="57" name="Signo más 56">
+          <xdr:cNvPr id="189" name="Signo más 188">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D67C64C6-0BC7-4A24-A6B9-18161965AA7B}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E925E33-1E79-49BB-8AC8-625C5465009D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3529,10 +5341,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="58" name="Imagen 57">
+          <xdr:cNvPr id="190" name="Imagen 189">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7ABDA51-19C2-40D9-AA7F-53F43055B125}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F3854D6-CE10-46D2-80A8-5CBD87BDC8BD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3541,20 +5353,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3574,23 +5386,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2074690</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>160084</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>84235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1093055</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>421340</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>459015</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="59" name="Grupo 58">
+        <xdr:cNvPr id="191" name="Grupo 190">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCCD8E4D-20DD-4028-B4EA-96380DC20383}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75CD88C2-198D-4228-AC88-AA0DB0FB6B51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3598,18 +5410,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4646440" y="8132509"/>
-          <a:ext cx="1094815" cy="261256"/>
+          <a:off x="4649107" y="9824681"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="60" name="Signo menos 59">
+          <xdr:cNvPr id="192" name="Signo menos 191">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE489E8-6253-476E-9E41-0CB9CDD38BC3}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BD96A30-8434-4D89-88CA-9D36EBA82FB2}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3658,10 +5470,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="61" name="Signo más 60">
+          <xdr:cNvPr id="193" name="Signo más 192">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA18E4FD-CA7C-4225-8373-6EE737E37E62}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF98E69-F767-46C4-A14F-1EBDF8E62271}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3710,10 +5522,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="62" name="Imagen 61">
+          <xdr:cNvPr id="194" name="Imagen 193">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{422D168E-E100-4557-96F7-C1076643C49A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7E1F86E-C4E8-42AB-B874-F0B1686C96F3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3722,20 +5534,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3756,22 +5568,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>19210</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>153681</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>129592</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1118668</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>414937</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>504372</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="63" name="Grupo 62">
+        <xdr:cNvPr id="195" name="Grupo 194">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{576D6996-5433-4FE3-9FE3-D5AC6FE9847A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99BFF723-1349-456D-B261-AC5DEEDB18B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3779,18 +5591,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4667410" y="9011931"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="10516378"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="64" name="Signo menos 63">
+          <xdr:cNvPr id="196" name="Signo menos 195">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CD1273C-F9DB-4DC4-84BF-124494B71C95}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{567F0E68-4A57-461D-A29E-D3C2AE10F31F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3839,10 +5651,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="65" name="Signo más 64">
+          <xdr:cNvPr id="197" name="Signo más 196">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6FACEB7-9147-483F-B27E-804FF57D11FE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1489017A-69E8-4D07-B274-EFF4A78BA35F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3891,10 +5703,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="66" name="Imagen 65">
+          <xdr:cNvPr id="198" name="Imagen 197">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40C0EE92-E2F6-453A-88BD-59E90E0901EB}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EECE1744-CA46-4DE6-A5EB-7509D3C69040}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3903,20 +5715,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3937,22 +5749,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>6404</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>192101</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>103673</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1105862</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>453357</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>18402</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="67" name="Grupo 66">
+        <xdr:cNvPr id="199" name="Grupo 198">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D09AD6C-80EA-4EC5-A290-D33AE2F54BBA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85AF2C7C-9D44-40F1-993C-1B13E27304EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3960,18 +5772,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4654604" y="9698051"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="11136798"/>
+          <a:ext cx="1128033" cy="368300"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="68" name="Signo menos 67">
+          <xdr:cNvPr id="200" name="Signo menos 199">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF1646CB-2BC6-490D-8594-3770D840575A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A7338FE-7211-4805-A3C1-FD7E7088B4E3}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4020,10 +5832,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="69" name="Signo más 68">
+          <xdr:cNvPr id="201" name="Signo más 200">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{399FBFFA-E595-4858-B255-F395EF585548}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FED59602-FAB7-45AB-8A14-027FD8EC3864}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4072,10 +5884,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="70" name="Imagen 69">
+          <xdr:cNvPr id="202" name="Imagen 201">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CE018E0-7791-422F-A86A-C49DA0FB3BFF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08F2F7B4-6B8A-4F30-A3FC-33579653107B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4084,20 +5896,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4117,23 +5929,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2074690</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>102454</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1093055</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>363710</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>50801</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="71" name="Grupo 70">
+        <xdr:cNvPr id="203" name="Grupo 202">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FA12DD-1E64-4B4F-9145-CE277F570D1F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05264E85-289F-4C63-AE98-7195EB4BE048}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4141,18 +5953,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4646440" y="10256104"/>
-          <a:ext cx="1094815" cy="261256"/>
+          <a:off x="4649107" y="15512143"/>
+          <a:ext cx="1128033" cy="504372"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="72" name="Signo menos 71">
+          <xdr:cNvPr id="204" name="Signo menos 203">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BA66669-2640-4B22-9CBC-06A1B7C0EDF1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA531C78-D61A-4598-B3D6-6AA40808E9C8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4201,10 +6013,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="73" name="Signo más 72">
+          <xdr:cNvPr id="205" name="Signo más 204">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7444876-2106-4ED5-BABD-A3BADF58C373}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E16BC8-470B-4BD4-B17A-BBF3C3D1808D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4253,10 +6065,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="74" name="Imagen 73">
+          <xdr:cNvPr id="206" name="Imagen 205">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07447FD3-681C-4DD2-8109-5EB075CF9427}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B8114FE-D11E-4B34-8D8C-711279A05298}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4265,20 +6077,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4301,20 +6113,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>51837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>261256</xdr:rowOff>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>76718</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="75" name="Grupo 74">
+        <xdr:cNvPr id="207" name="Grupo 206">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5789BA8-B251-423F-B30D-3727950AB2CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{064909C2-5E31-4289-9506-3104B6BE66B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4322,18 +6134,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648200" y="14306550"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="16017551"/>
+          <a:ext cx="1128033" cy="489792"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="76" name="Signo menos 75">
+          <xdr:cNvPr id="208" name="Signo menos 207">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9266D062-8FE8-442E-B756-AF7ECA615D3C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A378E349-E553-400C-91B4-B5DA99C96652}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4382,10 +6194,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="77" name="Signo más 76">
+          <xdr:cNvPr id="209" name="Signo más 208">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5B1CB53-1D1A-42BD-B1D6-E6364900429A}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16E9E3DE-6154-47AD-A7C3-46C3E323A184}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4434,10 +6246,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="78" name="Imagen 77">
+          <xdr:cNvPr id="210" name="Imagen 209">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AD757B2-68AF-494E-A895-D58357F27BD4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E38D9A8C-6976-4017-940A-16A8CB36578B}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4446,20 +6258,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4480,22 +6292,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>11526</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>107577</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>110152</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1110984</xdr:colOff>
+      <xdr:colOff>1137558</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>368833</xdr:rowOff>
+      <xdr:rowOff>25918</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="79" name="Grupo 78">
+        <xdr:cNvPr id="211" name="Grupo 210">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8FDEC04-F7A5-4D02-B3A1-2541E4450C6C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{755ADF28-F0BB-4E80-AC2B-EEA7C2F32EAA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4503,18 +6315,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4659726" y="15138027"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="16540777"/>
+          <a:ext cx="1128033" cy="357998"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="80" name="Signo menos 79">
+          <xdr:cNvPr id="212" name="Signo menos 211">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{492B1A65-25D6-4826-B697-ADEFC323775E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0CD94EA-5828-441C-B2CD-F01A8AC245FC}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4563,10 +6375,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="81" name="Signo más 80">
+          <xdr:cNvPr id="213" name="Signo más 212">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22412B97-FE2D-4891-8789-BD60B4D28B66}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0001E5AE-8F3F-4A9F-B7FD-4F0C4B535DE9}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4615,10 +6427,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="82" name="Imagen 81">
+          <xdr:cNvPr id="214" name="Imagen 213">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E16B799-D039-4275-ABFE-A34D8E345E33}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF2056EF-7629-4064-B5AC-1BF1421C0BEA}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4627,20 +6439,382 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>97194</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>471974</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="215" name="Grupo 214">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59400143-8D5D-4A0C-9126-8C2084D5101E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4649107" y="16970051"/>
+          <a:ext cx="1128033" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="216" name="Signo menos 215">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D223EDB-E79C-4ECD-98CF-A6E02D58178F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="217" name="Signo más 216">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B4D97B1-4A23-4791-8978-2830A4921471}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="218" name="Imagen 217">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2314298-65A2-4B34-99CF-F52C55B2EDC0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:extLst>
+            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123112</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1137558</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>497892</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="219" name="Grupo 218">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4DA6BB5-21F3-4E59-A620-3DCAAC3979AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4649107" y="17608291"/>
+          <a:ext cx="1128033" cy="374780"/>
+          <a:chOff x="393577" y="132100"/>
+          <a:chExt cx="2836472" cy="961027"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="220" name="Signo menos 219">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED6134ED-9AC2-45AA-8C45-796BEB210826}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="393577" y="361215"/>
+            <a:ext cx="341454" cy="208344"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathMinus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="221" name="Signo más 220">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37A3B954-64AB-4F0D-A5D6-534F09A73F5E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2993194" y="366696"/>
+            <a:ext cx="236855" cy="288924"/>
+          </a:xfrm>
+          <a:prstGeom prst="mathPlus">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="222" name="Imagen 221">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B5B9D30-FC57-4B9E-9E01-0A35CFCD2CEC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4663,20 +6837,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>71276</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
+      <xdr:colOff>1137558</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>261256</xdr:rowOff>
+      <xdr:rowOff>446056</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="83" name="Grupo 82">
+        <xdr:cNvPr id="223" name="Grupo 222">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F403D813-43C2-4DEC-A81B-FBD49418F910}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19576C98-2C90-4A43-B31B-FE4889E016CD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4684,18 +6858,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648200" y="15830550"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="18282169"/>
+          <a:ext cx="1128033" cy="374780"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="84" name="Signo menos 83">
+          <xdr:cNvPr id="224" name="Signo menos 223">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66D080F3-7AC1-4366-84CD-2A814ED215D6}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFBAE702-78B9-442C-91FD-088BE00F4738}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4744,10 +6918,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="85" name="Signo más 84">
+          <xdr:cNvPr id="225" name="Signo más 224">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ED40455-3915-4EDC-8CFB-E24F73B295A3}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB4AFB2F-31A3-46CA-BC7E-707CCA526E1F}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4796,10 +6970,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="86" name="Imagen 85">
+          <xdr:cNvPr id="226" name="Imagen 225">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F408D07-1688-4EEB-A97A-2F5F4879F9B1}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F21D91C1-6C75-4C13-8599-A5555EF2A2CB}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4808,20 +6982,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4848,16 +7022,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
+      <xdr:colOff>1137558</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>261256</xdr:rowOff>
+      <xdr:rowOff>356377</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="87" name="Grupo 86">
+        <xdr:cNvPr id="227" name="Grupo 226">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E9FC7BE-793E-475C-B5B4-F56B0C5D44B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C82BE6-41D3-4930-9DD2-9F8ED84C5DEC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4865,18 +7039,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4648200" y="16287750"/>
-          <a:ext cx="1099458" cy="261256"/>
+          <a:off x="4649107" y="18936607"/>
+          <a:ext cx="1128033" cy="356377"/>
           <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
+          <a:chExt cx="2836472" cy="961027"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="88" name="Signo menos 87">
+          <xdr:cNvPr id="228" name="Signo menos 227">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC31E3F2-0CFA-4369-946D-9905ECF9ED03}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{264BAE7C-BD0A-4CBB-91F5-A9E74A4790A8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4925,10 +7099,10 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="89" name="Signo más 88">
+          <xdr:cNvPr id="229" name="Signo más 228">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9428A06F-70ED-4239-87B0-A626D8AC6631}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E4392B6-C7D2-4F6F-8568-476D1A039254}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4977,10 +7151,10 @@
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="90" name="Imagen 89">
+          <xdr:cNvPr id="230" name="Imagen 229">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0EF1F0B-9C64-4E18-92C7-E8D4723240E0}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77ECB7AB-2481-4229-A3D4-860FCEC7195C}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4989,563 +7163,20 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
               </a:ext>
             </a:extLst>
           </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
+          <a:srcRect l="8458" t="48227" r="61845" b="29780"/>
           <a:stretch/>
         </xdr:blipFill>
         <xdr:spPr bwMode="auto">
           <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>261256</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="91" name="Grupo 90">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23983253-13C6-462C-BF90-FC258D54AF7A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4648200" y="15487650"/>
-          <a:ext cx="1099458" cy="261256"/>
-          <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="92" name="Signo menos 91">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34899D12-56CE-4EB4-9C2F-B6E8B97999D7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="393577" y="361215"/>
-            <a:ext cx="341454" cy="208344"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathMinus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="93" name="Signo más 92">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48FF5D7A-9086-46D7-9214-DD290D246A43}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2993194" y="366696"/>
-            <a:ext cx="236855" cy="288924"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathPlus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="00B050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="94" name="Imagen 93">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC8787E-A152-45EA-B211-E2E13036120E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
-          <a:stretch/>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>261256</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="95" name="Grupo 94">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF2A179A-135A-422C-8ABE-D7205A504D91}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4648200" y="13963650"/>
-          <a:ext cx="1099458" cy="261256"/>
-          <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="96" name="Signo menos 95">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F7663D-DEDE-4304-968E-BBB65AD5B755}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="393577" y="361215"/>
-            <a:ext cx="341454" cy="208344"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathMinus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="97" name="Signo más 96">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF54E822-519E-4F62-B5CD-8C2FADFB6023}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2993194" y="366696"/>
-            <a:ext cx="236855" cy="288924"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathPlus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="00B050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="98" name="Imagen 97">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{243CDADB-F47F-4778-8DFD-F9395DFEF3F7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
-          <a:stretch/>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-              <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1099458</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>261256</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="99" name="Grupo 98">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF5C759B-C208-44F4-97F1-C1AB7C950458}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="4648200" y="14649450"/>
-          <a:ext cx="1099458" cy="261256"/>
-          <a:chOff x="393577" y="132100"/>
-          <a:chExt cx="2836472" cy="795328"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="100" name="Signo menos 99">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAC9A5EE-9608-4D7E-A0C3-678613F3D6E0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="393577" y="361215"/>
-            <a:ext cx="341454" cy="208344"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathMinus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="101" name="Signo más 100">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01750CE9-E55B-4210-9EF3-0E6AD1EBD423}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2993194" y="366696"/>
-            <a:ext cx="236855" cy="288924"/>
-          </a:xfrm>
-          <a:prstGeom prst="mathPlus">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="00B050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="102" name="Imagen 101">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10ACE857-D42C-4150-8045-D1F18F56B2AC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect l="8458" t="48226" r="61845" b="33573"/>
-          <a:stretch/>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="700779" y="132100"/>
-            <a:ext cx="2308099" cy="795328"/>
+            <a:off x="700778" y="132100"/>
+            <a:ext cx="2308100" cy="961027"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5567,9 +7198,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5607,7 +7238,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5713,7 +7344,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5855,7 +7486,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5864,969 +7495,953 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F699AF-E3F2-43F2-9698-269D4B8C0237}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="7" width="22.5703125" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="28" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="22.35" customHeight="1">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:13" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+    </row>
+    <row r="2" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+    </row>
+    <row r="3" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="105"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
     </row>
-    <row r="2" spans="1:13" ht="12" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="84" t="s">
+    <row r="5" spans="1:13" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="80"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+    </row>
+    <row r="6" spans="1:13" ht="13.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="1:13" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="86"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="96"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="87"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="83"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="53"/>
+      <c r="B10" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:13" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="53"/>
+      <c r="B11" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="72"/>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="59"/>
+    </row>
+    <row r="12" spans="1:13" ht="68.650000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="53"/>
+      <c r="B12" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="73"/>
+      <c r="E12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="59"/>
+    </row>
+    <row r="13" spans="1:13" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="53"/>
+      <c r="B13" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="73"/>
+      <c r="E13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="59"/>
+    </row>
+    <row r="14" spans="1:13" ht="42.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="54"/>
+      <c r="B14" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="59"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="85"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
     </row>
-    <row r="3" spans="1:13" ht="12" customHeight="1" thickBot="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="80"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="99" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="100"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
     </row>
-    <row r="4" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="B4" s="93" t="s">
+    <row r="19" spans="1:9" ht="10.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="92" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="93"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="88"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="96"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="89"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+    </row>
+    <row r="22" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="53"/>
+      <c r="B23" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="53"/>
+      <c r="B24" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="72"/>
+      <c r="E24" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" spans="1:9" ht="41.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="53"/>
+      <c r="B25" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" spans="1:9" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="53"/>
+      <c r="B26" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="73"/>
+      <c r="E26" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" spans="1:9" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="53"/>
+      <c r="B27" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="73"/>
+      <c r="E27" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="I27" s="13"/>
+    </row>
+    <row r="28" spans="1:9" ht="47.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="53"/>
+      <c r="B28" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" spans="1:9" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="53"/>
+      <c r="B29" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="53"/>
+      <c r="B30" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="54"/>
+      <c r="B31" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="66" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="85"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="103"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="40"/>
+    </row>
+    <row r="34" spans="1:9" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="106" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="107"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="99" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="100"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
     </row>
-    <row r="5" spans="1:13" ht="9.6" customHeight="1">
-      <c r="B5" s="96" t="s">
+    <row r="35" spans="1:9" ht="12.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="34"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="93"/>
+      <c r="G35" s="94"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
     </row>
-    <row r="6" spans="1:13" ht="13.35" customHeight="1" thickBot="1">
-      <c r="B6" s="99" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33" t="s">
+      <c r="B36" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="96"/>
+      <c r="G36" s="97"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
     </row>
-    <row r="7" spans="1:13" ht="14.65" customHeight="1">
-      <c r="A7" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="109" t="s">
+    <row r="37" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="110"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="63" t="s">
+    <row r="38" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="83"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="53"/>
+      <c r="B39" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="88" t="s">
+      <c r="F39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="19" t="s">
+      <c r="G39" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
     </row>
-    <row r="9" spans="1:13" ht="27" customHeight="1">
-      <c r="A9" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="90" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="90"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+    <row r="40" spans="1:9" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="53"/>
+      <c r="B40" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="72"/>
+      <c r="E40" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
     </row>
-    <row r="10" spans="1:13" ht="27" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
+    <row r="41" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="53"/>
+      <c r="B41" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="73"/>
+      <c r="E41" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="41.65" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="77"/>
+    <row r="42" spans="1:9" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="53"/>
+      <c r="B42" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="73"/>
+      <c r="E42" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
     </row>
-    <row r="12" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="77"/>
+    <row r="43" spans="1:9" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="53"/>
+      <c r="B43" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="73"/>
+      <c r="E43" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="F43" s="68" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
     </row>
-    <row r="13" spans="1:13" ht="44.65" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="77"/>
+    <row r="44" spans="1:9" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="53"/>
+      <c r="B44" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="75"/>
+      <c r="E44" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
     </row>
-    <row r="14" spans="1:13" ht="42.95" customHeight="1" thickBot="1">
-      <c r="A14" s="66"/>
-      <c r="B14" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="77"/>
+    <row r="45" spans="1:9" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="53"/>
+      <c r="B45" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="75"/>
+      <c r="E45" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="69" t="s">
+        <v>125</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
     </row>
-    <row r="15" spans="1:13">
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
+    <row r="46" spans="1:9" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="53"/>
+      <c r="B46" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="75"/>
+      <c r="E46" s="69" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46" s="69" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
     </row>
-    <row r="16" spans="1:13" ht="15" thickBot="1">
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
+    <row r="47" spans="1:9" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="53"/>
+      <c r="B47" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" s="75"/>
+      <c r="E47" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F47" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="G47" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
     </row>
-    <row r="17" spans="1:9">
-      <c r="B17" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="94"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="106" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="107"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
+    <row r="48" spans="1:9" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="53"/>
+      <c r="B48" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" s="76"/>
+      <c r="E48" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="F48" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="G48" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
     </row>
-    <row r="18" spans="1:9">
-      <c r="B18" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="85" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="86"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
+    <row r="49" spans="1:7" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="53"/>
+      <c r="B49" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D49" s="77"/>
+      <c r="E49" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="F49" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" s="69" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="19" spans="1:9" ht="10.7" customHeight="1" thickBot="1">
-      <c r="B19" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="100"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="79"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="81" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="109" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="110"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-    </row>
-    <row r="21" spans="1:9" ht="18" customHeight="1">
-      <c r="A21" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="88"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" ht="36" customHeight="1">
-      <c r="A22" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="65"/>
-      <c r="B23" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="1:9" ht="44.1" customHeight="1">
-      <c r="A24" s="65"/>
-      <c r="B24" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="16"/>
-    </row>
-    <row r="25" spans="1:9" ht="41.65" customHeight="1">
-      <c r="A25" s="65"/>
-      <c r="B25" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="16"/>
-    </row>
-    <row r="26" spans="1:9" ht="51.95" customHeight="1">
-      <c r="A26" s="65"/>
-      <c r="B26" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" s="16"/>
-    </row>
-    <row r="27" spans="1:9" ht="51.95" customHeight="1">
-      <c r="A27" s="65"/>
-      <c r="B27" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="16"/>
-    </row>
-    <row r="28" spans="1:9" ht="18" customHeight="1">
-      <c r="A28" s="65"/>
-      <c r="B28" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I28" s="16"/>
-    </row>
-    <row r="29" spans="1:9" ht="51.6" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" s="37"/>
-      <c r="E29" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I29" s="16"/>
-    </row>
-    <row r="30" spans="1:9" ht="51.6" customHeight="1">
-      <c r="A30" s="65"/>
-      <c r="B30" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="37"/>
-      <c r="E30" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="16"/>
-    </row>
-    <row r="31" spans="1:9" ht="36" customHeight="1" thickBot="1">
-      <c r="A31" s="66"/>
-      <c r="B31" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="67" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="38"/>
-      <c r="E31" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="16"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.4" thickBot="1">
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="16"/>
-    </row>
-    <row r="33" spans="1:9" ht="15">
-      <c r="B33" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="94"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="106" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="107"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="49"/>
-    </row>
-    <row r="34" spans="1:9" ht="8.65" customHeight="1">
-      <c r="B34" s="96" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="97"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="85" t="s">
-        <v>91</v>
-      </c>
-      <c r="F34" s="86"/>
-      <c r="G34" s="87"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-    </row>
-    <row r="35" spans="1:9" ht="12.4" customHeight="1" thickBot="1">
-      <c r="B35" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="100"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="F35" s="79"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="82"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="82"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-    </row>
-    <row r="37" spans="1:9" ht="14.65" customHeight="1">
-      <c r="A37" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="88" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-    </row>
-    <row r="38" spans="1:9" ht="36" customHeight="1">
-      <c r="A38" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="90" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="65"/>
-      <c r="B39" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-    </row>
-    <row r="40" spans="1:9" ht="27">
-      <c r="A40" s="65"/>
-      <c r="B40" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="73"/>
-      <c r="E40" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-    </row>
-    <row r="41" spans="1:9" ht="36">
-      <c r="A41" s="65"/>
-      <c r="B41" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" s="73"/>
-      <c r="E41" s="76" t="s">
-        <v>105</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-    </row>
-    <row r="42" spans="1:9" ht="36">
-      <c r="A42" s="65"/>
-      <c r="B42" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" s="73"/>
-      <c r="E42" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-    </row>
-    <row r="43" spans="1:9" ht="36">
-      <c r="A43" s="65"/>
-      <c r="B43" s="69" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" s="73"/>
-      <c r="E43" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-    </row>
-    <row r="44" spans="1:9" ht="27">
-      <c r="A44" s="65"/>
-      <c r="B44" s="69" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" s="73"/>
-      <c r="E44" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-    </row>
-    <row r="45" spans="1:9" ht="27">
-      <c r="A45" s="65"/>
-      <c r="B45" s="69" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" s="74"/>
-      <c r="E45" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-    </row>
-    <row r="46" spans="1:9" ht="30" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D46" s="74"/>
-      <c r="E46" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-    </row>
-    <row r="47" spans="1:9" ht="36">
-      <c r="A47" s="65"/>
-      <c r="B47" s="69" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-    </row>
-    <row r="48" spans="1:9" ht="27.4" thickBot="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="70" t="s">
-        <v>138</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G48" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-    </row>
-    <row r="49" spans="1:7" ht="36.4" thickBot="1">
-      <c r="A49" s="65"/>
-      <c r="B49" s="70" t="s">
-        <v>143</v>
-      </c>
-      <c r="C49" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="F49" s="3" t="s">
+    <row r="50" spans="1:7" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="54"/>
+      <c r="B50" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="G49" s="27" t="s">
+      <c r="C50" s="71" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="27.4" thickBot="1">
-      <c r="A50" s="66"/>
-      <c r="B50" s="70" t="s">
+      <c r="D50" s="78"/>
+      <c r="E50" s="69" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="F50" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="D50" s="75"/>
-      <c r="E50" s="24" t="s">
+      <c r="G50" s="70" t="s">
         <v>150</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="J1:M2"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E20:G20"/>
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="E34:G34"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
